--- a/data/processed_data/40V_2/contracciones_40V_2.xlsx
+++ b/data/processed_data/40V_2/contracciones_40V_2.xlsx
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF2"/>
+  <dimension ref="A1:CS2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1209,6 +1209,71 @@
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_cinetica_n_pulsos</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_reportable</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ms</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ic95_ms</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_reportable</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ms</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ic95_ms</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_cota_ms</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>forzada_periodo_origen</t>
         </is>
@@ -1452,7 +1517,38 @@
       <c r="CE2" t="n">
         <v>0.02839067446646426</v>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="n">
+        <v>183.3333333333229</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>6</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="n">
+        <v>183.3333333333229</v>
+      </c>
+      <c r="CS2" t="inlineStr">
         <is>
           <t>1/0.1 Hz +-2 %</t>
         </is>
@@ -1469,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,6 +1584,36 @@
           <t>responde</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_ms</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1499,6 +1625,24 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
+      <c r="D2" t="n">
+        <v>117.9609179920348</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>199.9999999999886</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55.92421725055146</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>133.3333333333258</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1510,6 +1654,24 @@
       <c r="C3" t="b">
         <v>1</v>
       </c>
+      <c r="D3" t="n">
+        <v>47.57168183128956</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>133.3333333333258</v>
+      </c>
+      <c r="G3" t="n">
+        <v>95.73734305142473</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>133.3333333333258</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1521,6 +1683,24 @@
       <c r="C4" t="b">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>45.02603538115793</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>166.6666666666572</v>
+      </c>
+      <c r="G4" t="n">
+        <v>102.7191395132822</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>166.6666666666572</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1532,6 +1712,24 @@
       <c r="C5" t="b">
         <v>1</v>
       </c>
+      <c r="D5" t="n">
+        <v>63.57084742235131</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>133.3333333333258</v>
+      </c>
+      <c r="G5" t="n">
+        <v>137.4871756394344</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>199.9999999999886</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1543,6 +1741,24 @@
       <c r="C6" t="b">
         <v>1</v>
       </c>
+      <c r="D6" t="n">
+        <v>93.31915259629298</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>199.9999999999886</v>
+      </c>
+      <c r="G6" t="n">
+        <v>106.0415000327181</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>199.9999999999886</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1553,6 +1769,24 @@
       </c>
       <c r="C7" t="b">
         <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>55.51328262437573</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>199.9999999999886</v>
+      </c>
+      <c r="G7" t="n">
+        <v>134.8563987730359</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>199.9999999999886</v>
       </c>
     </row>
   </sheetData>
